--- a/scripts/Fig2/vertical_smage.xlsx
+++ b/scripts/Fig2/vertical_smage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\scmgca\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\周泽铭\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD517320-381F-4DDB-98A7-7DC6AAC90F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480B1AE2-87F5-43D7-9592-B8D2F5B14A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -411,7 +411,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,6 +456,21 @@
       <sz val="11"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -506,7 +521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -538,6 +553,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1576,16 +1603,16 @@
       <c r="CD3" s="2">
         <v>7.2222</v>
       </c>
-      <c r="CE3" t="s">
+      <c r="CE3" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="CF3" t="s">
+      <c r="CF3" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="CG3" t="s">
+      <c r="CG3" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="CH3" t="s">
+      <c r="CH3" s="13" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1836,16 +1863,16 @@
       <c r="CD4" s="2">
         <v>6.6666999999999996</v>
       </c>
-      <c r="CE4" t="s">
+      <c r="CE4" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="CF4" t="s">
+      <c r="CF4" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="CG4" t="s">
+      <c r="CG4" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="CH4" t="s">
+      <c r="CH4" s="13" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2096,16 +2123,16 @@
       <c r="CD5" s="2">
         <v>9.7777999999999992</v>
       </c>
-      <c r="CE5" t="s">
+      <c r="CE5" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="CF5" t="s">
+      <c r="CF5" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="CG5" t="s">
+      <c r="CG5" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CH5" t="s">
+      <c r="CH5" s="13" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2356,16 +2383,16 @@
       <c r="CD6" s="2">
         <v>7.5556000000000001</v>
       </c>
-      <c r="CE6" t="s">
+      <c r="CE6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="CF6" t="s">
+      <c r="CF6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="CG6" t="s">
+      <c r="CG6" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="CH6" t="s">
+      <c r="CH6" s="13" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2616,16 +2643,16 @@
       <c r="CD7" s="2">
         <v>6</v>
       </c>
-      <c r="CE7" t="s">
+      <c r="CE7" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CF7" t="s">
+      <c r="CF7" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CG7" t="s">
+      <c r="CG7" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CH7" t="s">
+      <c r="CH7" s="13" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2876,16 +2903,16 @@
       <c r="CD8" s="2">
         <v>8.3332999999999995</v>
       </c>
-      <c r="CE8" t="s">
+      <c r="CE8" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CF8" t="s">
+      <c r="CF8" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CG8" t="s">
+      <c r="CG8" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CH8" t="s">
+      <c r="CH8" s="13" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3136,16 +3163,16 @@
       <c r="CD9" s="2">
         <v>16.333300000000001</v>
       </c>
-      <c r="CE9" t="s">
+      <c r="CE9" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CF9" t="s">
+      <c r="CF9" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CG9" t="s">
+      <c r="CG9" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CH9" t="s">
+      <c r="CH9" s="13" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3396,17 +3423,17 @@
       <c r="CD10" s="2">
         <v>13.777799999999999</v>
       </c>
-      <c r="CE10" t="s">
-        <v>62</v>
-      </c>
-      <c r="CF10" t="s">
-        <v>62</v>
-      </c>
-      <c r="CG10" t="s">
-        <v>112</v>
-      </c>
-      <c r="CH10" t="s">
-        <v>112</v>
+      <c r="CE10" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="CF10" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="CG10" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="CH10" s="15" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:86" ht="15.6" x14ac:dyDescent="0.25">
@@ -3656,16 +3683,16 @@
       <c r="CD11" s="2">
         <v>11.666700000000001</v>
       </c>
-      <c r="CE11" t="s">
-        <v>112</v>
-      </c>
-      <c r="CF11" t="s">
-        <v>112</v>
-      </c>
-      <c r="CG11" t="s">
-        <v>112</v>
-      </c>
-      <c r="CH11" t="s">
+      <c r="CE11" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="CF11" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="CG11" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="CH11" s="13" t="s">
         <v>61</v>
       </c>
     </row>
@@ -3916,16 +3943,16 @@
       <c r="CD12" s="2">
         <v>14.777799999999999</v>
       </c>
-      <c r="CE12" t="s">
+      <c r="CE12" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="CF12" t="s">
+      <c r="CF12" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="CG12" t="s">
-        <v>113</v>
-      </c>
-      <c r="CH12" t="s">
+      <c r="CG12" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="CH12" s="13" t="s">
         <v>113</v>
       </c>
     </row>
@@ -4176,16 +4203,16 @@
       <c r="CD13" s="2">
         <v>11.222200000000001</v>
       </c>
-      <c r="CE13" t="s">
+      <c r="CE13" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="CF13" t="s">
+      <c r="CF13" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CG13" t="s">
+      <c r="CG13" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CH13" t="s">
+      <c r="CH13" s="13" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4436,17 +4463,17 @@
       <c r="CD14" s="2">
         <v>7.5556000000000001</v>
       </c>
-      <c r="CE14" t="s">
+      <c r="CE14" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="CF14" t="s">
-        <v>63</v>
-      </c>
-      <c r="CG14" t="s">
-        <v>63</v>
-      </c>
-      <c r="CH14" t="s">
-        <v>63</v>
+      <c r="CF14" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="CG14" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="CH14" s="15" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:86" ht="15.6" x14ac:dyDescent="0.25">
@@ -4696,16 +4723,16 @@
       <c r="CD15" s="2">
         <v>14</v>
       </c>
-      <c r="CE15" t="s">
+      <c r="CE15" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CF15" t="s">
+      <c r="CF15" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CG15" t="s">
+      <c r="CG15" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="CH15" t="s">
+      <c r="CH15" s="13" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4956,16 +4983,16 @@
       <c r="CD16" s="2">
         <v>15.8889</v>
       </c>
-      <c r="CE16" t="s">
+      <c r="CE16" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CF16" t="s">
+      <c r="CF16" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CG16" t="s">
-        <v>62</v>
-      </c>
-      <c r="CH16" t="s">
+      <c r="CG16" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="CH16" s="13" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5216,16 +5243,16 @@
       <c r="CD17" s="2">
         <v>6.5556000000000001</v>
       </c>
-      <c r="CE17" t="s">
+      <c r="CE17" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CF17" t="s">
+      <c r="CF17" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CG17" t="s">
+      <c r="CG17" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CH17" t="s">
+      <c r="CH17" s="13" t="s">
         <v>63</v>
       </c>
     </row>
@@ -5476,16 +5503,16 @@
       <c r="CD18" s="2">
         <v>18.222200000000001</v>
       </c>
-      <c r="CE18" t="s">
+      <c r="CE18" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CF18" t="s">
+      <c r="CF18" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CG18" t="s">
+      <c r="CG18" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CH18" t="s">
+      <c r="CH18" s="13" t="s">
         <v>62</v>
       </c>
     </row>
@@ -5736,16 +5763,16 @@
       <c r="CD19" s="2">
         <v>8</v>
       </c>
-      <c r="CE19" t="s">
+      <c r="CE19" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CF19" t="s">
+      <c r="CF19" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CG19" t="s">
+      <c r="CG19" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CH19" t="s">
+      <c r="CH19" s="13" t="s">
         <v>63</v>
       </c>
     </row>
@@ -5996,16 +6023,16 @@
       <c r="CD20" s="2">
         <v>6</v>
       </c>
-      <c r="CE20" t="s">
+      <c r="CE20" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CF20" t="s">
+      <c r="CF20" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CG20" t="s">
+      <c r="CG20" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="CH20" t="s">
+      <c r="CH20" s="13" t="s">
         <v>63</v>
       </c>
     </row>
@@ -6256,16 +6283,16 @@
       <c r="CD21" s="2">
         <v>15.1111</v>
       </c>
-      <c r="CE21" t="s">
+      <c r="CE21" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CF21" t="s">
+      <c r="CF21" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CG21" t="s">
+      <c r="CG21" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="CH21" t="s">
+      <c r="CH21" s="13" t="s">
         <v>62</v>
       </c>
     </row>
